--- a/data/trans_bre/P16A09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,66</t>
+          <t>1,27; 5,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,76</t>
+          <t>6,51; 10,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,1</t>
+          <t>3,57; 8,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,91</t>
+          <t>5,72; 11,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 99,94</t>
+          <t>17,32; 102,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>119,45; 352,59</t>
+          <t>126,36; 354,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,8; 309,1</t>
+          <t>71,66; 309,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>94,5; 315,38</t>
+          <t>88,32; 311,29</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,32</t>
+          <t>-0,34; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,35</t>
+          <t>-0,26; 1,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,87</t>
+          <t>0,27; 1,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,5</t>
+          <t>0,54; 2,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 158,01</t>
+          <t>-22,77; 148,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 138,09</t>
+          <t>-15,82; 153,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,55; 307,58</t>
+          <t>16,2; 315,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,73; 211,78</t>
+          <t>24,61; 217,83</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,15</t>
+          <t>-0,44; 3,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,66</t>
+          <t>-1,86; 1,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,82</t>
+          <t>0,19; 1,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,0</t>
+          <t>1,78; 4,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 624,61</t>
+          <t>-39,38; 728,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>-78,8; 338,94</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>122,6; —</t>
+          <t>206,09; —</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,08</t>
+          <t>1,18; 3,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,6</t>
+          <t>2,79; 4,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,22</t>
+          <t>1,7; 3,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,22</t>
+          <t>2,27; 4,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,77; 123,17</t>
+          <t>34,83; 123,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>106,87; 263,52</t>
+          <t>110,57; 265,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>105,76; 300,14</t>
+          <t>100,12; 299,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>113,4; 305,9</t>
+          <t>110,97; 291,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,25</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>177,9%</t>
+          <t>183,31%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,62</t>
+          <t>1,43; 5,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,84</t>
+          <t>6,35; 10,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,09</t>
+          <t>3,48; 8,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,15</t>
+          <t>5,75; 10,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,32; 102,34</t>
+          <t>17,52; 107,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>126,36; 354,24</t>
+          <t>122,41; 354,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,66; 309,67</t>
+          <t>72,44; 295,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,32; 311,29</t>
+          <t>97,94; 312,53</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>100,5%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,33</t>
+          <t>-0,27; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,45</t>
+          <t>-0,3; 1,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,81</t>
+          <t>0,28; 1,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,47</t>
+          <t>1,02; 2,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 148,98</t>
+          <t>-17,65; 180,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 153,08</t>
+          <t>-20,36; 145,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,2; 315,92</t>
+          <t>19,22; 319,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,61; 217,83</t>
+          <t>44,92; 185,62</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1271,93%</t>
+          <t>1629,62%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,12</t>
+          <t>-0,3; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,62</t>
+          <t>-1,93; 1,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,93</t>
+          <t>0,2; 1,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,11</t>
+          <t>2,01; 4,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 728,62</t>
+          <t>-40,02; 622,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,8; 338,94</t>
+          <t>-75,8; 262,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>206,09; —</t>
+          <t>269,68; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>187,81%</t>
+          <t>189,76%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,15</t>
+          <t>1,2; 3,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,62</t>
+          <t>2,76; 4,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,27</t>
+          <t>1,81; 3,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,17</t>
+          <t>2,71; 4,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,83; 123,14</t>
+          <t>34,95; 124,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>110,57; 265,36</t>
+          <t>107,62; 268,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,12; 299,3</t>
+          <t>108,72; 317,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>110,97; 291,08</t>
+          <t>119,48; 273,51</t>
         </is>
       </c>
     </row>
